--- a/data.xlsx
+++ b/data.xlsx
@@ -1144,7 +1144,6 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="3"/>
       <c r="F2" s="2">
         <v>19</v>
       </c>
@@ -1380,7 +1379,6 @@
       <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>23</v>
       </c>
@@ -1410,7 +1408,6 @@
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>0</v>
       </c>
@@ -1434,7 +1431,6 @@
       <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="3"/>
       <c r="F12" s="2">
         <v>0</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Model</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Next Order</t>
+  </si>
+  <si>
+    <t>Next Order Date</t>
   </si>
   <si>
     <t>Next ETA</t>
@@ -1079,7 +1082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.1111111111111" style="2" customWidth="1"/>
@@ -1091,11 +1094,11 @@
     <col min="8" max="8" width="10" style="3" customWidth="1"/>
     <col min="9" max="9" width="13" style="3" customWidth="1"/>
     <col min="10" max="10" width="6.33333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.7777777777778" style="3"/>
-    <col min="12" max="12" width="9" style="2"/>
+    <col min="11" max="12" width="10.7777777777778" style="3"/>
+    <col min="13" max="13" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1129,14 +1132,17 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
@@ -1160,12 +1166,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>8</v>
@@ -1192,15 +1198,18 @@
         <v>10</v>
       </c>
       <c r="K3" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L3" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2">
         <v>8</v>
@@ -1227,15 +1236,18 @@
         <v>5</v>
       </c>
       <c r="K4" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L4" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -1253,15 +1265,18 @@
         <v>10</v>
       </c>
       <c r="K5" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L5" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1279,15 +1294,18 @@
         <v>10</v>
       </c>
       <c r="K6" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L6" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1305,12 +1323,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1337,15 +1355,18 @@
         <v>2</v>
       </c>
       <c r="K8" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L8" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
@@ -1363,15 +1384,18 @@
         <v>4</v>
       </c>
       <c r="K9" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L9" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -1395,12 +1419,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -1415,15 +1439,18 @@
         <v>2</v>
       </c>
       <c r="K11" s="3">
+        <v>46127</v>
+      </c>
+      <c r="L11" s="3">
         <v>46207</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -1438,12 +1465,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
         <v>7</v>
@@ -1458,12 +1485,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -1478,12 +1505,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -1498,12 +1525,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
@@ -1520,10 +1547,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
@@ -1540,10 +1567,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" r:id="rId1"/>
@@ -1160,7 +1160,7 @@
         <v>46127</v>
       </c>
       <c r="I2" s="3">
-        <v>46172</v>
+        <v>46183</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="3">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="F3" s="2">
         <v>12</v>
@@ -1192,16 +1192,17 @@
         <v>46127</v>
       </c>
       <c r="I3" s="3">
-        <v>46172</v>
+        <v>46183</v>
       </c>
       <c r="J3" s="2">
         <v>10</v>
       </c>
       <c r="K3" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L3" s="3">
-        <v>46207</v>
+        <f>K3+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1218,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="3">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="F4" s="2">
         <v>8</v>
@@ -1230,16 +1231,17 @@
         <v>46127</v>
       </c>
       <c r="I4" s="3">
-        <v>46172</v>
+        <v>46183</v>
       </c>
       <c r="J4" s="2">
         <v>5</v>
       </c>
       <c r="K4" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L4" s="3">
-        <v>46207</v>
+        <f>K4+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1256,7 +1258,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="3">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -1265,10 +1267,11 @@
         <v>10</v>
       </c>
       <c r="K5" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L5" s="3">
-        <v>46207</v>
+        <f>K5+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1285,7 +1288,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="3">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -1294,10 +1297,11 @@
         <v>10</v>
       </c>
       <c r="K6" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L6" s="3">
-        <v>46207</v>
+        <f>K6+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1314,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="3">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -1349,16 +1353,17 @@
         <v>46127</v>
       </c>
       <c r="I8" s="3">
-        <v>46172</v>
+        <v>46183</v>
       </c>
       <c r="J8" s="2">
         <v>2</v>
       </c>
       <c r="K8" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L8" s="3">
-        <v>46207</v>
+        <f>K8+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1384,10 +1389,11 @@
         <v>4</v>
       </c>
       <c r="K9" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L9" s="3">
-        <v>46207</v>
+        <f>K9+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1404,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G10" s="3">
         <v>46092</v>
@@ -1413,10 +1419,17 @@
         <v>46127</v>
       </c>
       <c r="I10" s="3">
-        <v>46172</v>
+        <v>46183</v>
       </c>
       <c r="J10" s="2">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="K10" s="3">
+        <v>46141</v>
+      </c>
+      <c r="L10" s="3">
+        <f>K10+45</f>
+        <v>46186</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1439,10 +1452,11 @@
         <v>2</v>
       </c>
       <c r="K11" s="3">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="L11" s="3">
-        <v>46207</v>
+        <f>K11+45</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="12" spans="1:13">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" r:id="rId1"/>
@@ -1157,10 +1157,11 @@
         <v>46092</v>
       </c>
       <c r="H2" s="3">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="I2" s="3">
-        <v>46183</v>
+        <f>H2+45</f>
+        <v>46188</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
@@ -1189,10 +1190,11 @@
         <v>46092</v>
       </c>
       <c r="H3" s="3">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="I3" s="3">
-        <v>46183</v>
+        <f t="shared" ref="I3:I8" si="0">H3+45</f>
+        <v>46188</v>
       </c>
       <c r="J3" s="2">
         <v>10</v>
@@ -1201,8 +1203,8 @@
         <v>46134</v>
       </c>
       <c r="L3" s="3">
-        <f>K3+45</f>
-        <v>46179</v>
+        <f t="shared" ref="L3:L6" si="1">K3+45+35</f>
+        <v>46214</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1228,10 +1230,11 @@
         <v>46092</v>
       </c>
       <c r="H4" s="3">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="I4" s="3">
-        <v>46183</v>
+        <f t="shared" si="0"/>
+        <v>46188</v>
       </c>
       <c r="J4" s="2">
         <v>5</v>
@@ -1240,8 +1243,8 @@
         <v>46134</v>
       </c>
       <c r="L4" s="3">
-        <f>K4+45</f>
-        <v>46179</v>
+        <f t="shared" si="1"/>
+        <v>46214</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1270,8 +1273,8 @@
         <v>46134</v>
       </c>
       <c r="L5" s="3">
-        <f>K5+45</f>
-        <v>46179</v>
+        <f t="shared" si="1"/>
+        <v>46214</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1300,8 +1303,8 @@
         <v>46134</v>
       </c>
       <c r="L6" s="3">
-        <f>K6+45</f>
-        <v>46179</v>
+        <f t="shared" si="1"/>
+        <v>46214</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1350,10 +1353,11 @@
         <v>46092</v>
       </c>
       <c r="H8" s="3">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="I8" s="3">
-        <v>46183</v>
+        <f t="shared" si="0"/>
+        <v>46188</v>
       </c>
       <c r="J8" s="2">
         <v>2</v>
@@ -1362,8 +1366,8 @@
         <v>46134</v>
       </c>
       <c r="L8" s="3">
-        <f>K8+45</f>
-        <v>46179</v>
+        <f t="shared" ref="L8:L11" si="2">K8+45+35</f>
+        <v>46214</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1392,8 +1396,8 @@
         <v>46134</v>
       </c>
       <c r="L9" s="3">
-        <f>K9+45</f>
-        <v>46179</v>
+        <f t="shared" si="2"/>
+        <v>46214</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1416,10 +1420,11 @@
         <v>46092</v>
       </c>
       <c r="H10" s="3">
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="I10" s="3">
-        <v>46183</v>
+        <f>H10+45</f>
+        <v>46188</v>
       </c>
       <c r="J10" s="2">
         <v>13</v>
@@ -1428,8 +1433,8 @@
         <v>46141</v>
       </c>
       <c r="L10" s="3">
-        <f>K10+45</f>
-        <v>46186</v>
+        <f t="shared" si="2"/>
+        <v>46221</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1455,8 +1460,8 @@
         <v>46134</v>
       </c>
       <c r="L11" s="3">
-        <f>K11+45</f>
-        <v>46179</v>
+        <f t="shared" si="2"/>
+        <v>46214</v>
       </c>
     </row>
     <row r="12" spans="1:13">

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" r:id="rId1"/>
@@ -1145,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -1175,14 +1175,12 @@
         <v>13</v>
       </c>
       <c r="C3" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3">
-        <v>46137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="2">
         <v>12</v>
       </c>
@@ -1215,14 +1213,12 @@
         <v>13</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3">
-        <v>46137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="2">
         <v>8</v>
       </c>
@@ -1255,14 +1251,12 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3">
-        <v>46137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="2">
         <v>0</v>
       </c>
@@ -1285,14 +1279,12 @@
         <v>13</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3">
-        <v>46137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>0</v>
       </c>
@@ -1315,14 +1307,12 @@
         <v>13</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>46137</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>0</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -29,11 +29,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>Model</t>
   </si>
   <si>
+    <t>Material Number</t>
+  </si>
+  <si>
     <t>Product Group</t>
   </si>
   <si>
@@ -70,58 +73,109 @@
     <t>LS0507EM</t>
   </si>
   <si>
+    <t>55F01390012B000</t>
+  </si>
+  <si>
     <t>Scissors</t>
   </si>
   <si>
     <t>LS0608E</t>
   </si>
   <si>
+    <t>55F02060007B000</t>
+  </si>
+  <si>
     <t>LS0808E</t>
   </si>
   <si>
+    <t>55F01480015B000</t>
+  </si>
+  <si>
     <t>LS0812E</t>
   </si>
   <si>
+    <t>55F01540011B000</t>
+  </si>
+  <si>
     <t>LS1012E</t>
   </si>
   <si>
+    <t>55F01500013B000</t>
+  </si>
+  <si>
     <t>LS1212E</t>
   </si>
   <si>
+    <t>55F01470012B000</t>
+  </si>
+  <si>
     <t>LS1412E</t>
   </si>
   <si>
+    <t>55F01850002B000</t>
+  </si>
+  <si>
     <t>LS1414E</t>
   </si>
   <si>
+    <t>55F02470006B000</t>
+  </si>
+  <si>
     <t>LS0610EC</t>
   </si>
   <si>
+    <t>55F02460008B000</t>
+  </si>
+  <si>
     <t>LS1216HC</t>
   </si>
   <si>
+    <t>55F01800003B000</t>
+  </si>
+  <si>
     <t>LS1623ERT</t>
   </si>
   <si>
+    <t>55F01700004B000</t>
+  </si>
+  <si>
     <t>LM09JE</t>
   </si>
   <si>
+    <t>55F02590012B000</t>
+  </si>
+  <si>
     <t>Boom</t>
   </si>
   <si>
     <t>LA14JE</t>
   </si>
   <si>
+    <t>55F01680006B000</t>
+  </si>
+  <si>
     <t>LA16JE</t>
   </si>
   <si>
+    <t>55F02140003B000</t>
+  </si>
+  <si>
     <t>LA20JE</t>
   </si>
   <si>
+    <t>55F01520002B000</t>
+  </si>
+  <si>
     <t>LT20JE</t>
   </si>
   <si>
+    <t>55F01120002B000</t>
+  </si>
+  <si>
     <t>LT26JE</t>
+  </si>
+  <si>
+    <t>55F01350002B000</t>
   </si>
 </sst>
 </file>
@@ -752,7 +806,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -768,8 +822,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1082,515 +1142,572 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1111111111111" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.55555555555556" style="2" customWidth="1"/>
-    <col min="3" max="4" width="6.33333333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.7777777777778" style="3"/>
-    <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="16.3333333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13" style="3" customWidth="1"/>
-    <col min="10" max="10" width="6.33333333333333" style="2" customWidth="1"/>
-    <col min="11" max="12" width="10.7777777777778" style="3"/>
-    <col min="13" max="13" width="9" style="2"/>
+    <col min="1" max="1" width="15.3518518518519" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.5833333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.55555555555556" style="2" customWidth="1"/>
+    <col min="4" max="5" width="6.33333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.7777777777778" style="3"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="16.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="10" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.21296296296296" style="2" customWidth="1"/>
+    <col min="12" max="13" width="10.7777777777778" style="3"/>
+    <col min="14" max="14" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:14">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="28.8" spans="1:14">
+      <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I2" s="3">
+        <v>46143</v>
+      </c>
+      <c r="J2" s="3">
+        <f>I2+45</f>
+        <v>46188</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="28.8" spans="1:14">
+      <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="H3" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I3" s="3">
+        <v>46143</v>
+      </c>
+      <c r="J3" s="3">
+        <f t="shared" ref="J3:J8" si="0">I3+45</f>
+        <v>46188</v>
+      </c>
+      <c r="K3" s="2">
+        <v>10</v>
+      </c>
+      <c r="L3" s="3">
+        <v>46134</v>
+      </c>
+      <c r="M3" s="3">
+        <f t="shared" ref="M3:M7" si="1">L3+45+35</f>
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:14">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3">
         <v>46092</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I4" s="3">
         <v>46143</v>
       </c>
-      <c r="I2" s="3">
-        <f>H2+45</f>
-        <v>46188</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="2">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3">
-        <v>46092</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46143</v>
-      </c>
-      <c r="I3" s="3">
-        <f t="shared" ref="I3:I8" si="0">H3+45</f>
-        <v>46188</v>
-      </c>
-      <c r="J3" s="2">
-        <v>10</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46134</v>
-      </c>
-      <c r="L3" s="3">
-        <f t="shared" ref="L3:L6" si="1">K3+45+35</f>
-        <v>46214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3">
-        <v>46092</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46143</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <f t="shared" si="0"/>
         <v>46188</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>5</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>46134</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2">
+    <row r="5" ht="28.8" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2">
         <v>18</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
         <v>10</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>46134</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
+    <row r="6" ht="28.8" spans="1:14">
+      <c r="A6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>10</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>46134</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <f t="shared" si="1"/>
         <v>46214</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
+    <row r="7" ht="28.8" spans="1:14">
+      <c r="A7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3</v>
+      </c>
+      <c r="L7" s="3">
+        <v>46134</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="1"/>
+        <v>46214</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
+    <row r="8" ht="28.8" spans="1:14">
+      <c r="A8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>2</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46158</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46092</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46143</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <f t="shared" si="0"/>
         <v>46188</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46134</v>
       </c>
-      <c r="L8" s="3">
-        <f t="shared" ref="L8:L11" si="2">K8+45+35</f>
+      <c r="M8" s="3">
+        <f t="shared" ref="M8:M11" si="2">L8+45+35</f>
         <v>46214</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
+    <row r="9" ht="28.8" spans="1:14">
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46158</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
         <v>4</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46134</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <f t="shared" si="2"/>
         <v>46214</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" ht="28.8" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46092</v>
+      </c>
+      <c r="I10" s="3">
+        <v>46143</v>
+      </c>
+      <c r="J10" s="3">
+        <f>I10+45</f>
+        <v>46188</v>
+      </c>
+      <c r="K10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3">
-        <v>46092</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46143</v>
-      </c>
-      <c r="I10" s="3">
-        <f>H10+45</f>
-        <v>46188</v>
-      </c>
-      <c r="J10" s="2">
-        <v>13</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>46141</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <f t="shared" si="2"/>
         <v>46221</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
+    <row r="11" ht="28.8" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
         <v>2</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>46134</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <f t="shared" si="2"/>
         <v>46214</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2">
+    <row r="12" ht="28.8" spans="1:14">
+      <c r="A12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2">
+    <row r="13" ht="28.8" spans="1:14">
+      <c r="A13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2">
         <v>7</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>8</v>
       </c>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2">
+    <row r="14" ht="28.8" spans="1:14">
+      <c r="A14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="2">
+    <row r="15" ht="28.8" spans="1:14">
+      <c r="A15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2">
+    <row r="16" ht="28.8" spans="1:14">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2">
         <v>3</v>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="2">
+    <row r="17" ht="28.8" spans="1:11">
+      <c r="A17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2">
         <v>3</v>
       </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="2">
+    <row r="18" ht="28.8" spans="1:11">
+      <c r="A18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="24048" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>Model</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Next ETA</t>
   </si>
   <si>
+    <t>Remark</t>
+  </si>
+  <si>
     <t>LS0507EM</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>55F02460008B000</t>
+  </si>
+  <si>
+    <t>Shipped as ordered</t>
   </si>
   <si>
     <t>LS1216HC</t>
@@ -806,7 +812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -818,9 +824,6 @@
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1142,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.3518518518519" style="2" customWidth="1"/>
@@ -1155,61 +1158,64 @@
     <col min="9" max="9" width="10" style="3" customWidth="1"/>
     <col min="10" max="10" width="13" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.21296296296296" style="2" customWidth="1"/>
-    <col min="12" max="13" width="10.7777777777778" style="3"/>
-    <col min="14" max="14" width="9" style="2"/>
+    <col min="12" max="14" width="10.7777777777778" style="3"/>
+    <col min="15" max="15" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6"/>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="5"/>
     </row>
-    <row r="2" ht="28.8" spans="1:14">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2">
         <v>6</v>
@@ -1234,15 +1240,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="28.8" spans="1:14">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="2">
         <v>4</v>
@@ -1267,22 +1273,22 @@
         <v>10</v>
       </c>
       <c r="L3" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" ref="M3:M7" si="1">L3+45+35</f>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:14">
-      <c r="A4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2">
         <v>13</v>
@@ -1307,22 +1313,22 @@
         <v>5</v>
       </c>
       <c r="L4" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M4" s="3">
         <f t="shared" si="1"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:14">
-      <c r="A5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:15">
+      <c r="A5" s="6" t="s">
         <v>21</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>18</v>
@@ -1337,22 +1343,22 @@
         <v>10</v>
       </c>
       <c r="L5" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="1"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="6" ht="28.8" spans="1:14">
-      <c r="A6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
+    <row r="6" spans="1:15">
+      <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1367,22 +1373,22 @@
         <v>10</v>
       </c>
       <c r="L6" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="1"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="7" ht="28.8" spans="1:14">
-      <c r="A7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:15">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="B7" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -1397,22 +1403,22 @@
         <v>3</v>
       </c>
       <c r="L7" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="1"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:14">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:15">
+      <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -1440,22 +1446,22 @@
         <v>2</v>
       </c>
       <c r="L8" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" ref="M8:M11" si="2">L8+45+35</f>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:14">
-      <c r="A9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="9" spans="1:15">
+      <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1473,22 +1479,22 @@
         <v>4</v>
       </c>
       <c r="L9" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="2"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:14">
-      <c r="A10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:15">
+      <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
@@ -1513,22 +1519,25 @@
         <v>13</v>
       </c>
       <c r="L10" s="3">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="2"/>
-        <v>46221</v>
+        <f>L10+45</f>
+        <v>46188</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:14">
-      <c r="A11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>33</v>
+    <row r="11" spans="1:15">
+      <c r="A11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -1543,22 +1552,22 @@
         <v>2</v>
       </c>
       <c r="L11" s="3">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="2"/>
-        <v>46214</v>
+        <v>46223</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:14">
-      <c r="A12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>35</v>
+    <row r="12" spans="1:15">
+      <c r="A12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1573,15 +1582,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:14">
-      <c r="A13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>37</v>
+    <row r="13" spans="1:15">
+      <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2">
         <v>7</v>
@@ -1596,15 +1605,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:14">
-      <c r="A14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="7" t="s">
+    <row r="14" spans="1:15">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1619,15 +1628,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:14">
-      <c r="A15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>42</v>
+    <row r="15" spans="1:15">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1642,15 +1651,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="28.8" spans="1:14">
-      <c r="A16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>44</v>
+    <row r="16" spans="1:15">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -1665,15 +1674,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:11">
-      <c r="A17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>46</v>
+    <row r="17" spans="1:11">
+      <c r="A17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1688,15 +1697,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:11">
-      <c r="A18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>48</v>
+    <row r="18" spans="1:11">
+      <c r="A18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>Model</t>
   </si>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t>55F01850002B000</t>
+  </si>
+  <si>
+    <t>Structure issue, on hold for selling</t>
   </si>
   <si>
     <t>LS1414E</t>
@@ -1443,22 +1446,20 @@
         <v>46188</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M8" s="3">
-        <f t="shared" ref="M8:M11" si="2">L8+45+35</f>
-        <v>46223</v>
+        <v>0</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1476,22 +1477,22 @@
         <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3">
         <v>46143</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M8:M11" si="2">L9+45+35</f>
         <v>46223</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1526,15 +1527,15 @@
         <v>46188</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>16</v>
@@ -1561,10 +1562,10 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>16</v>
@@ -1584,13 +1585,13 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2">
         <v>7</v>
@@ -1607,13 +1608,13 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1630,13 +1631,13 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1653,13 +1654,13 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -1676,13 +1677,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1699,13 +1700,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24048" windowHeight="12300"/>
+    <workbookView windowWidth="26331" windowHeight="12548"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>Model</t>
   </si>
@@ -118,9 +118,6 @@
     <t>55F01850002B000</t>
   </si>
   <si>
-    <t>Structure issue, on hold for selling</t>
-  </si>
-  <si>
     <t>LS1414E</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
   </si>
   <si>
     <t>55F02460008B000</t>
-  </si>
-  <si>
-    <t>Shipped as ordered</t>
   </si>
   <si>
     <t>LS1216HC</t>
@@ -1149,23 +1143,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="15.3518518518519" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.5833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.55555555555556" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.3513513513514" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.5855855855856" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.55855855855856" style="2" customWidth="1"/>
     <col min="4" max="5" width="6.33333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.7777777777778" style="3"/>
+    <col min="6" max="6" width="10.7747747747748" style="3"/>
     <col min="7" max="7" width="9" style="2"/>
     <col min="8" max="8" width="16.3333333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="10" style="3" customWidth="1"/>
     <col min="10" max="10" width="13" style="3" customWidth="1"/>
-    <col min="11" max="11" width="8.21296296296296" style="2" customWidth="1"/>
-    <col min="12" max="14" width="10.7777777777778" style="3"/>
+    <col min="11" max="11" width="8.21621621621622" style="2" customWidth="1"/>
+    <col min="12" max="14" width="10.7747747747748" style="3"/>
     <col min="15" max="15" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="43.2" spans="1:15">
+    <row r="1" s="1" customFormat="1" ht="42.45" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1204,7 @@
       </c>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" ht="14.15" spans="1:15">
       <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
@@ -1221,29 +1215,22 @@
         <v>16</v>
       </c>
       <c r="D2" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2">
-        <v>19</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46143</v>
-      </c>
-      <c r="J2" s="3">
-        <f>I2+45</f>
-        <v>46188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" ht="14.15" spans="1:15">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
@@ -1254,36 +1241,29 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3">
-        <v>46092</v>
+        <v>46149</v>
       </c>
       <c r="I3" s="3">
-        <v>46143</v>
+        <v>46183</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J8" si="0">I3+45</f>
-        <v>46188</v>
+        <f t="shared" ref="J3:J7" si="0">I3+45</f>
+        <v>46228</v>
       </c>
       <c r="K3" s="2">
-        <v>10</v>
-      </c>
-      <c r="L3" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M3" s="3">
-        <f t="shared" ref="M3:M7" si="1">L3+45+35</f>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" ht="14.15" spans="1:15">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
@@ -1297,33 +1277,26 @@
         <v>13</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H4" s="3">
-        <v>46092</v>
+        <v>46149</v>
       </c>
       <c r="I4" s="3">
-        <v>46143</v>
+        <v>46183</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="0"/>
-        <v>46188</v>
+        <v>46228</v>
       </c>
       <c r="K4" s="2">
-        <v>5</v>
-      </c>
-      <c r="L4" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M4" s="3">
-        <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" ht="14.15" spans="1:15">
       <c r="A5" s="6" t="s">
         <v>21</v>
       </c>
@@ -1340,20 +1313,23 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I5" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" si="0"/>
+        <v>46228</v>
       </c>
       <c r="K5" s="2">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M5" s="3">
-        <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" ht="14.15" spans="1:15">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -1370,20 +1346,23 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="0"/>
+        <v>46228</v>
       </c>
       <c r="K6" s="2">
-        <v>10</v>
-      </c>
-      <c r="L6" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" ht="14.15" spans="1:15">
       <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
@@ -1400,20 +1379,23 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>46228</v>
       </c>
       <c r="K7" s="2">
-        <v>3</v>
-      </c>
-      <c r="L7" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M7" s="3">
-        <f t="shared" si="1"/>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" ht="14.15" spans="1:15">
       <c r="A8" s="6" t="s">
         <v>27</v>
       </c>
@@ -1424,42 +1406,28 @@
         <v>16</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46158</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46143</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="0"/>
-        <v>46188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3" t="s">
+    </row>
+    <row r="9" ht="14.15" spans="1:15">
+      <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1468,31 +1436,32 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>46158</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" ref="J9:J13" si="1">I9+45</f>
+        <v>46228</v>
       </c>
       <c r="K9" s="2">
-        <v>6</v>
-      </c>
-      <c r="L9" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M9" s="3">
-        <f t="shared" ref="M8:M11" si="2">L9+45+35</f>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" ht="14.15" spans="1:15">
       <c r="A10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1501,41 +1470,24 @@
         <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G10" s="2">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46092</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46143</v>
-      </c>
-      <c r="J10" s="3">
-        <f>I10+45</f>
-        <v>46188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="2">
-        <v>13</v>
-      </c>
-      <c r="L10" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M10" s="3">
-        <f>L10+45</f>
-        <v>46188</v>
-      </c>
-      <c r="N10" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="14.15" spans="1:15">
+      <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>16</v>
@@ -1547,25 +1499,28 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="1"/>
+        <v>46228</v>
       </c>
       <c r="K11" s="2">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3">
-        <v>46143</v>
-      </c>
-      <c r="M11" s="3">
-        <f t="shared" si="2"/>
-        <v>46223</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" ht="14.15" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>16</v>
@@ -1583,15 +1538,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" ht="14.15" spans="1:15">
       <c r="A13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D13" s="2">
         <v>7</v>
@@ -1602,19 +1557,29 @@
       <c r="G13" s="2">
         <v>8</v>
       </c>
+      <c r="H13" s="3">
+        <v>46149</v>
+      </c>
+      <c r="I13" s="3">
+        <v>46183</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="1"/>
+        <v>46228</v>
+      </c>
       <c r="K13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" ht="14.15" spans="1:15">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1629,15 +1594,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" ht="14.15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1652,15 +1617,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" ht="14.15" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -1675,15 +1640,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" ht="14.15" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1698,15 +1663,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" ht="14.15" spans="1:11">
       <c r="A18" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
@@ -1732,7 +1697,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1744,7 +1709,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1223,9 +1223,6 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
       <c r="K2" s="2">
         <v>0</v>
       </c>
@@ -1411,13 +1408,9 @@
       <c r="E8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="3"/>
       <c r="G8" s="2">
         <v>0</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
       <c r="K8" s="2">
         <v>0</v>
       </c>
@@ -1438,7 +1431,6 @@
       <c r="E9" s="2">
         <v>0</v>
       </c>
-      <c r="F9" s="3"/>
       <c r="G9" s="2">
         <v>6</v>
       </c>
@@ -1475,9 +1467,6 @@
       <c r="G10" s="2">
         <v>0</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
       <c r="K10" s="2">
         <v>0</v>
       </c>
@@ -1552,20 +1541,20 @@
         <v>7</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2">
         <v>8</v>
       </c>
       <c r="H13" s="3">
-        <v>46149</v>
+        <v>46120</v>
       </c>
       <c r="I13" s="3">
-        <v>46183</v>
+        <v>46153</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
-        <v>46228</v>
+        <v>46198</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>Model</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Scissors</t>
   </si>
   <si>
+    <t>5 are arriving in 24/06/2026</t>
+  </si>
+  <si>
     <t>LS0608E</t>
   </si>
   <si>
@@ -128,6 +131,9 @@
   </si>
   <si>
     <t>55F02460008B000</t>
+  </si>
+  <si>
+    <t>13 are arriving in 24/06/2026</t>
   </si>
   <si>
     <t>LS1216HC</t>
@@ -809,7 +815,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -829,6 +835,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1155,7 +1164,8 @@
     <col min="9" max="9" width="10" style="3" customWidth="1"/>
     <col min="10" max="10" width="13" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.21621621621622" style="2" customWidth="1"/>
-    <col min="12" max="14" width="10.7747747747748" style="3"/>
+    <col min="12" max="13" width="10.7747747747748" style="3"/>
+    <col min="14" max="14" width="30" style="3" customWidth="1"/>
     <col min="15" max="15" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1220,19 +1230,25 @@
       <c r="E2" s="2">
         <v>19</v>
       </c>
+      <c r="F2" s="3">
+        <v>46203</v>
+      </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="14.15" spans="1:15">
       <c r="A3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -1242,6 +1258,9 @@
       </c>
       <c r="E3" s="2">
         <v>12</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46203</v>
       </c>
       <c r="G3" s="2">
         <v>20</v>
@@ -1262,10 +1281,10 @@
     </row>
     <row r="4" ht="14.15" spans="1:15">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>16</v>
@@ -1275,6 +1294,9 @@
       </c>
       <c r="E4" s="2">
         <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46203</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -1295,10 +1317,10 @@
     </row>
     <row r="5" ht="14.15" spans="1:15">
       <c r="A5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
@@ -1328,10 +1350,10 @@
     </row>
     <row r="6" ht="14.15" spans="1:15">
       <c r="A6" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>16</v>
@@ -1361,10 +1383,10 @@
     </row>
     <row r="7" ht="14.15" spans="1:15">
       <c r="A7" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>16</v>
@@ -1394,10 +1416,10 @@
     </row>
     <row r="8" ht="14.15" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
@@ -1417,10 +1439,10 @@
     </row>
     <row r="9" ht="14.15" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1450,10 +1472,10 @@
     </row>
     <row r="10" ht="14.15" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1464,19 +1486,25 @@
       <c r="E10" s="2">
         <v>23</v>
       </c>
+      <c r="F10" s="3">
+        <v>46203</v>
+      </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="14.15" spans="1:15">
       <c r="A11" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>16</v>
@@ -1506,10 +1534,10 @@
     </row>
     <row r="12" ht="14.15" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>16</v>
@@ -1529,19 +1557,22 @@
     </row>
     <row r="13" ht="14.15" spans="1:15">
       <c r="A13" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2">
         <v>7</v>
       </c>
       <c r="E13" s="2">
         <v>8</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46182</v>
       </c>
       <c r="G13" s="2">
         <v>8</v>
@@ -1562,13 +1593,13 @@
     </row>
     <row r="14" ht="14.15" spans="1:15">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1585,13 +1616,13 @@
     </row>
     <row r="15" ht="14.15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1608,13 +1639,13 @@
     </row>
     <row r="16" ht="14.15" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -1631,13 +1662,13 @@
     </row>
     <row r="17" ht="14.15" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1654,13 +1685,13 @@
     </row>
     <row r="18" ht="14.15" spans="1:11">
       <c r="A18" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
